--- a/analises/vinhos/2026-10-13-portugal-fornecedores-acima-200.xlsx
+++ b/analises/vinhos/2026-10-13-portugal-fornecedores-acima-200.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sem info de estoque" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Com estoque'!$A$2:$H$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Com estoque'!$A$2:$H$345</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sem info de estoque'!$A$2:$H$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -449,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vinhos de Portugal, custo final &gt; R$ 200, estoque &gt; 0 (Mistral e World Wine: unidades; Epice: preço publicado = disponível; Del Maipo especiais: unidades). Fontes locais em dados/fornecedores.</t>
+          <t>Vinhos de Portugal, custo final &gt; R$ 200, estoque &gt; 0 (Tanyno: preço tabela A37 e estoque da planilha de 03/09; Mistral e World Wine: unidades; Epice: preço publicado = disponível; Del Maipo especiais: unidades). Fontes locais em dados/fornecedores.</t>
         </is>
       </c>
     </row>
@@ -10950,17 +10950,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Rocim Bela Luz Douro Vinhas Velhas</t>
+          <t>Monte Xisto Órbita</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Nicolau De Almeida</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -10975,30 +10975,30 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G277" s="3" t="n">
-        <v>207.87</v>
+        <v>247.78</v>
       </c>
       <c r="H277" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>CARM Gouveio</t>
+          <t>Eremitas Amon De Kelia</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Carm</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11013,30 +11013,30 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G278" s="3" t="n">
-        <v>215.4</v>
+        <v>247.78</v>
       </c>
       <c r="H278" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Maçanita Reserva Branco</t>
+          <t>Eremitas Antão Do Deserto</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Maçanita</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11051,30 +11051,30 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G279" s="3" t="n">
-        <v>215.4</v>
+        <v>247.78</v>
       </c>
       <c r="H279" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Maçanita a Laranja do Norte é tão boa!</t>
+          <t>Eremitas Paulo De Tebas</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Maçanita</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11093,31 +11093,31 @@
         </is>
       </c>
       <c r="G280" s="3" t="n">
-        <v>215.4</v>
+        <v>247.78</v>
       </c>
       <c r="H280" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Rocim Bela Luz</t>
+          <t>Rumo Incerto</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Rumo Vinhos</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Douro</t>
+          <t>Alentejo</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -11127,35 +11127,35 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G281" s="3" t="n">
-        <v>231.54</v>
+        <v>263.73</v>
       </c>
       <c r="H281" t="n">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Barão do Hospital Reserva Alvarinho</t>
+          <t>Rumo Lumina</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Falua</t>
+          <t>Rumo Vinhos</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Vinho Verde</t>
+          <t>Alentejo</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11165,30 +11165,30 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G282" s="3" t="n">
-        <v>242.4</v>
+        <v>263.73</v>
       </c>
       <c r="H282" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Quinta do Pessegueiro DOC</t>
+          <t>Curral Teles Alpha</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Quinta do Pessegueiro</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -11203,30 +11203,30 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>N.V.</t>
         </is>
       </c>
       <c r="G283" s="3" t="n">
-        <v>258.6</v>
+        <v>306.53</v>
       </c>
       <c r="H283" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Quinta do Pessegueiro DOC</t>
+          <t>Curral Teles Zeta</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Quinta do Pessegueiro</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -11241,149 +11241,149 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G284" s="3" t="n">
-        <v>258.6</v>
+        <v>306.53</v>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Rocim O Estrangeiro Tinto</t>
+          <t>Rumo Lumia</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Rumo Vinhos</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Dão</t>
+          <t>Alentejo</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Tinto</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G285" s="3" t="n">
-        <v>264</v>
+        <v>330.02</v>
       </c>
       <c r="H285" t="n">
-        <v>32</v>
+        <v>145</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Rocim O Estrangeiro Branco</t>
+          <t>Ruby Seco</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Dão</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Fortificado</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>N.V.</t>
         </is>
       </c>
       <c r="G286" s="3" t="n">
-        <v>264</v>
+        <v>345.69</v>
       </c>
       <c r="H286" t="n">
-        <v>23</v>
+        <v>88</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Rocim Santiago na Ânfora do Rocim Alvarinho</t>
+          <t>Lágrima 500Ml</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Mateus Nicolau</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Vinho Verde</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Fortificado</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>N.V.</t>
         </is>
       </c>
       <c r="G287" s="3" t="n">
-        <v>269.12</v>
+        <v>345.69</v>
       </c>
       <c r="H287" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Quinta da Falorca Reserva Lagar</t>
+          <t>Rumo Lumina</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Quinta da Falorca</t>
+          <t>Rumo Vinhos</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Dão</t>
+          <t>Alentejo</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -11393,30 +11393,30 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G288" s="3" t="n">
-        <v>269.4</v>
+        <v>373.81</v>
       </c>
       <c r="H288" t="n">
-        <v>146</v>
+        <v>231</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Quinta Nova Rosé Colheita DOC (1500ml)</t>
+          <t>Vintage</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Quinta Nova Nossa Senhora do Carmo</t>
+          <t>Nicolau De Almeida</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11426,16 +11426,16 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Fortificado</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G289" s="3" t="n">
-        <v>279.33</v>
+        <v>590.17</v>
       </c>
       <c r="H289" t="n">
         <v>1</v>
@@ -11444,22 +11444,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Autoral</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Quinta da Falorca Touriga Nacional</t>
+          <t>Quinta Do Monte Xisto Oriente</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Quinta da Falorca</t>
+          <t>Nicolau De Almeida</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Dão</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -11469,35 +11469,35 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G290" s="3" t="n">
-        <v>296.4</v>
+        <v>600.27</v>
       </c>
       <c r="H290" t="n">
-        <v>108</v>
+        <v>39</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>CARM Maria de Lourdes Tinto DOC</t>
+          <t>The Grenache</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Carm</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Douro</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -11507,35 +11507,35 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G291" s="3" t="n">
-        <v>353.4</v>
+        <v>215.68</v>
       </c>
       <c r="H291" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Rocim Terracotta Clay Aged Tinto</t>
+          <t>Protagonista</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Alentejo</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -11549,200 +11549,200 @@
         </is>
       </c>
       <c r="G292" s="3" t="n">
-        <v>366</v>
+        <v>313.65</v>
       </c>
       <c r="H292" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Azores Wine Company Arinto dos Açores 2ª Edição Estágio Prolongado 48 meses</t>
+          <t>Antagonista</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Azores Wine Company</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Açores</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G293" s="3" t="n">
-        <v>379.52</v>
+        <v>316.32</v>
       </c>
       <c r="H293" t="n">
-        <v>218</v>
+        <v>80</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Azores Wine Company Arinto dos Açores Sur Lies</t>
+          <t>Resiliente</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Azores Wine Company</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Açores</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G294" s="3" t="n">
-        <v>379.52</v>
+        <v>674.8099999999999</v>
       </c>
       <c r="H294" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Maçanita Quanto + Arinto + Gosto de ti</t>
+          <t>The Syrah</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Maçanita</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Douro</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="G295" s="3" t="n">
-        <v>426</v>
+        <v>759.15</v>
       </c>
       <c r="H295" t="n">
-        <v>268</v>
+        <v>35</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Herdade Aldeia de Cima Garrafeira Branco</t>
+          <t>The Touriga Nacional</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Herdade Aldeia de Cima</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Alentejo</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="G296" s="3" t="n">
-        <v>442.2</v>
+        <v>759.15</v>
       </c>
       <c r="H296" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>World Wine</t>
+          <t>Tanyno Signature</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Krohn Porto Vintage</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Wiese &amp; Krohn</t>
+          <t>Pinhal Da Torre</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Tejo</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G297" s="3" t="n">
-        <v>455.18</v>
+        <v>1096.57</v>
       </c>
       <c r="H297" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="298">
@@ -11753,17 +11753,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Herdade Aldeia de Cima Alyantiju Tinto</t>
+          <t>Rocim Bela Luz Douro Vinhas Velhas</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Herdade Aldeia de Cima</t>
+          <t>Herdade do Rocim</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Alentejo</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -11773,14 +11773,14 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G298" s="3" t="n">
-        <v>458.9</v>
+        <v>207.87</v>
       </c>
       <c r="H298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -11791,12 +11791,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Quinta Nova Mirabilis Branco DOC</t>
+          <t>CARM Gouveio</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Quinta Nova Nossa Senhora do Carmo</t>
+          <t>Carm</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -11811,14 +11811,14 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G299" s="3" t="n">
-        <v>485.4</v>
+        <v>215.4</v>
       </c>
       <c r="H299" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="300">
@@ -11829,12 +11829,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Quinta Nova Mirabilis Branco DOC</t>
+          <t>Maçanita Reserva Branco</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Quinta Nova Nossa Senhora do Carmo</t>
+          <t>Maçanita</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -11849,14 +11849,14 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G300" s="3" t="n">
-        <v>485.4</v>
+        <v>215.4</v>
       </c>
       <c r="H300" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="301">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Quinta Nova Mirabilis Branco DOC</t>
+          <t>Maçanita a Laranja do Norte é tão boa!</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Quinta Nova Nossa Senhora do Carmo</t>
+          <t>Maçanita</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -11887,14 +11887,14 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G301" s="3" t="n">
-        <v>485.4</v>
+        <v>215.4</v>
       </c>
       <c r="H301" t="n">
-        <v>280</v>
+        <v>113</v>
       </c>
     </row>
     <row r="302">
@@ -11905,22 +11905,22 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Azores Wine Company Terrantez do Pico</t>
+          <t>Rocim Bela Luz</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Azores Wine Company</t>
+          <t>Herdade do Rocim</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Açores</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="G302" s="3" t="n">
-        <v>563.84</v>
+        <v>231.54</v>
       </c>
       <c r="H302" t="n">
-        <v>105</v>
+        <v>22</v>
       </c>
     </row>
     <row r="303">
@@ -11943,34 +11943,34 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Fonseca Porto Vintage "Guimaraens"</t>
+          <t>Barão do Hospital Reserva Alvarinho</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Falua</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Vinho Verde</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G303" s="3" t="n">
-        <v>642.6</v>
+        <v>242.4</v>
       </c>
       <c r="H303" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Quinta da Falorca Garrafeira Old Vines</t>
+          <t>Quinta do Pessegueiro DOC</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Quinta da Falorca</t>
+          <t>Quinta do Pessegueiro</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Dão</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -12001,14 +12001,14 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="G304" s="3" t="n">
-        <v>642.6</v>
+        <v>258.6</v>
       </c>
       <c r="H304" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="305">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Taboadella Grande Villae Tinto</t>
+          <t>Quinta do Pessegueiro DOC</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Taboadella</t>
+          <t>Quinta do Pessegueiro</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Dão</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -12039,14 +12039,14 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G305" s="3" t="n">
-        <v>642.6</v>
+        <v>258.6</v>
       </c>
       <c r="H305" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -12057,31 +12057,31 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Fonseca Porto Vintage</t>
+          <t>Rocim O Estrangeiro Tinto</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Herdade do Rocim</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Dão</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G306" s="3" t="n">
-        <v>697.8</v>
+        <v>264</v>
       </c>
       <c r="H306" t="n">
         <v>32</v>
@@ -12095,34 +12095,34 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Casa Santa Eufêmia Porto 30 Anos</t>
+          <t>Rocim O Estrangeiro Branco</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Casa Santa Eufêmia</t>
+          <t>Herdade do Rocim</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Dão</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G307" s="3" t="n">
-        <v>735.36</v>
+        <v>264</v>
       </c>
       <c r="H307" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308">
@@ -12133,34 +12133,34 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>CARM "CM"</t>
+          <t>Rocim Santiago na Ânfora do Rocim Alvarinho</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Carm</t>
+          <t>Herdade do Rocim</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Douro</t>
+          <t>Vinho Verde</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Tinto</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G308" s="3" t="n">
-        <v>750.6</v>
+        <v>269.12</v>
       </c>
       <c r="H308" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309">
@@ -12171,34 +12171,34 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Fonseca Porto Vintage</t>
+          <t>Quinta da Falorca Reserva Lagar</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Quinta da Falorca</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Dão</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="G309" s="3" t="n">
-        <v>750.6</v>
+        <v>269.4</v>
       </c>
       <c r="H309" t="n">
-        <v>25</v>
+        <v>146</v>
       </c>
     </row>
     <row r="310">
@@ -12209,34 +12209,34 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Rocim Grande Reserva DOC</t>
+          <t>Quinta Nova Rosé Colheita DOC (1500ml)</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Quinta Nova Nossa Senhora do Carmo</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Alentejo</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Tinto</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G310" s="3" t="n">
-        <v>793.8</v>
+        <v>279.33</v>
       </c>
       <c r="H310" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -12247,17 +12247,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Rocim Grande Reserva DOC</t>
+          <t>Quinta da Falorca Touriga Nacional</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Quinta da Falorca</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Alentejo</t>
+          <t>Dão</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12267,14 +12267,14 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G311" s="3" t="n">
-        <v>793.8</v>
+        <v>296.4</v>
       </c>
       <c r="H311" t="n">
-        <v>51</v>
+        <v>108</v>
       </c>
     </row>
     <row r="312">
@@ -12285,17 +12285,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Herdade Aldeia de Cima Garrafeira Tinto</t>
+          <t>CARM Maria de Lourdes Tinto DOC</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Herdade Aldeia de Cima</t>
+          <t>Carm</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Alentejo</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -12305,14 +12305,14 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G312" s="3" t="n">
-        <v>890.4</v>
+        <v>353.4</v>
       </c>
       <c r="H312" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="313">
@@ -12323,34 +12323,34 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Azores Wine Company Canada do Monte</t>
+          <t>Rocim Terracotta Clay Aged Tinto</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Azores Wine Company</t>
+          <t>Herdade do Rocim</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Açores</t>
+          <t>Alentejo</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G313" s="3" t="n">
-        <v>973.4400000000001</v>
+        <v>366</v>
       </c>
       <c r="H313" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Azores Wine Company Vinha Centenária</t>
+          <t>Azores Wine Company Arinto dos Açores 2ª Edição Estágio Prolongado 48 meses</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12381,14 +12381,14 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G314" s="3" t="n">
-        <v>1031.04</v>
+        <v>379.52</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>218</v>
       </c>
     </row>
     <row r="315">
@@ -12399,17 +12399,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Maçanita Pala Pinta Branco</t>
+          <t>Azores Wine Company Arinto dos Açores Sur Lies</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Maçanita</t>
+          <t>Azores Wine Company</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Douro</t>
+          <t>Açores</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12419,14 +12419,14 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G315" s="3" t="n">
-        <v>1064.96</v>
+        <v>379.52</v>
       </c>
       <c r="H315" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
     </row>
     <row r="316">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Quinta Nova Mirabilis Tinto DOC</t>
+          <t>Maçanita Quanto + Arinto + Gosto de ti</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Quinta Nova Nossa Senhora do Carmo</t>
+          <t>Maçanita</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -12452,19 +12452,19 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Tinto</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G316" s="3" t="n">
-        <v>1560.6</v>
+        <v>426</v>
       </c>
       <c r="H316" t="n">
-        <v>10</v>
+        <v>268</v>
       </c>
     </row>
     <row r="317">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Rocim Vinha da Micaela</t>
+          <t>Herdade Aldeia de Cima Garrafeira Branco</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Herdade do Rocim</t>
+          <t>Herdade Aldeia de Cima</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -12490,19 +12490,19 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Tinto</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G317" s="3" t="n">
-        <v>1928.96</v>
+        <v>442.2</v>
       </c>
       <c r="H317" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="318">
@@ -12533,14 +12533,14 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G318" s="3" t="n">
-        <v>2672.64</v>
+        <v>455.18</v>
       </c>
       <c r="H318" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -12551,34 +12551,34 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Krohn Porto Vintage</t>
+          <t>Herdade Aldeia de Cima Alyantiju Tinto</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Wiese &amp; Krohn</t>
+          <t>Herdade Aldeia de Cima</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Alentejo</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Tinto</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G319" s="3" t="n">
-        <v>2839.68</v>
+        <v>458.9</v>
       </c>
       <c r="H319" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -12589,34 +12589,34 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Krohn Porto Vintage</t>
+          <t>Quinta Nova Mirabilis Branco DOC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Wiese &amp; Krohn</t>
+          <t>Quinta Nova Nossa Senhora do Carmo</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G320" s="3" t="n">
-        <v>3173.76</v>
+        <v>485.4</v>
       </c>
       <c r="H320" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -12627,34 +12627,34 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Krohn Porto Vintage</t>
+          <t>Quinta Nova Mirabilis Branco DOC</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Wiese &amp; Krohn</t>
+          <t>Quinta Nova Nossa Senhora do Carmo</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3454.97</v>
+        <v>485.4</v>
       </c>
       <c r="H321" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -12665,34 +12665,34 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Krohn Porto Vintage</t>
+          <t>Quinta Nova Mirabilis Branco DOC</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Wiese &amp; Krohn</t>
+          <t>Quinta Nova Nossa Senhora do Carmo</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Douro</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="G322" s="3" t="n">
-        <v>3507.84</v>
+        <v>485.4</v>
       </c>
       <c r="H322" t="n">
-        <v>61</v>
+        <v>280</v>
       </c>
     </row>
     <row r="323">
@@ -12703,34 +12703,34 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Krohn Porto Vintage</t>
+          <t>Azores Wine Company Terrantez do Pico</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Wiese &amp; Krohn</t>
+          <t>Azores Wine Company</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Porto (Douro)</t>
+          <t>Açores</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Fortificado</t>
+          <t>Branco</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G323" s="3" t="n">
-        <v>3716.64</v>
+        <v>563.84</v>
       </c>
       <c r="H323" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
     </row>
     <row r="324">
@@ -12741,38 +12741,836 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
+          <t>Fonseca Porto Vintage "Guimaraens"</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G324" s="3" t="n">
+        <v>642.6</v>
+      </c>
+      <c r="H324" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Quinta da Falorca Garrafeira Old Vines</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Quinta da Falorca</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G325" s="3" t="n">
+        <v>642.6</v>
+      </c>
+      <c r="H325" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Taboadella Grande Villae Tinto</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Taboadella</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Dão</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G326" s="3" t="n">
+        <v>642.6</v>
+      </c>
+      <c r="H326" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Fonseca Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G327" s="3" t="n">
+        <v>697.8</v>
+      </c>
+      <c r="H327" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Casa Santa Eufêmia Porto 30 Anos</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Casa Santa Eufêmia</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G328" s="3" t="n">
+        <v>735.36</v>
+      </c>
+      <c r="H328" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>CARM "CM"</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Carm</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Douro</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G329" s="3" t="n">
+        <v>750.6</v>
+      </c>
+      <c r="H329" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Fonseca Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="G330" s="3" t="n">
+        <v>750.6</v>
+      </c>
+      <c r="H330" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Rocim Grande Reserva DOC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Herdade do Rocim</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Alentejo</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G331" s="3" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="H331" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Rocim Grande Reserva DOC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Herdade do Rocim</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Alentejo</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="H332" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Herdade Aldeia de Cima Garrafeira Tinto</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Herdade Aldeia de Cima</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Alentejo</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="n">
+        <v>890.4</v>
+      </c>
+      <c r="H333" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Azores Wine Company Canada do Monte</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Azores Wine Company</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Açores</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Branco</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="n">
+        <v>973.4400000000001</v>
+      </c>
+      <c r="H334" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Azores Wine Company Vinha Centenária</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Azores Wine Company</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Açores</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Branco</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="n">
+        <v>1031.04</v>
+      </c>
+      <c r="H335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Maçanita Pala Pinta Branco</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Maçanita</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Douro</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Branco</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="n">
+        <v>1064.96</v>
+      </c>
+      <c r="H336" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Quinta Nova Mirabilis Tinto DOC</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Quinta Nova Nossa Senhora do Carmo</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Douro</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="n">
+        <v>1560.6</v>
+      </c>
+      <c r="H337" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Rocim Vinha da Micaela</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Herdade do Rocim</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Alentejo</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="n">
+        <v>1928.96</v>
+      </c>
+      <c r="H338" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Krohn Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Wiese &amp; Krohn</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="n">
+        <v>2672.64</v>
+      </c>
+      <c r="H339" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Krohn Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Wiese &amp; Krohn</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="n">
+        <v>2839.68</v>
+      </c>
+      <c r="H340" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Krohn Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Wiese &amp; Krohn</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="n">
+        <v>3173.76</v>
+      </c>
+      <c r="H341" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Krohn Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Wiese &amp; Krohn</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="G342" s="3" t="n">
+        <v>3454.97</v>
+      </c>
+      <c r="H342" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Krohn Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Wiese &amp; Krohn</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="n">
+        <v>3507.84</v>
+      </c>
+      <c r="H343" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Krohn Porto Vintage</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Wiese &amp; Krohn</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Porto (Douro)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Fortificado</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="n">
+        <v>3716.64</v>
+      </c>
+      <c r="H344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>World Wine</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
           <t>Rocim Júpiter Tinto</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
+      <c r="C345" t="inlineStr">
         <is>
           <t>Herdade do Rocim</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
+      <c r="D345" t="inlineStr">
         <is>
           <t>Alentejo</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>Tinto</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Tinto</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="G324" s="3" t="n">
+      <c r="G345" s="3" t="n">
         <v>10828.8</v>
       </c>
-      <c r="H324" t="n">
+      <c r="H345" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H324"/>
+  <autoFilter ref="A2:H345"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
